--- a/Excel/035-portfolio.xlsx
+++ b/Excel/035-portfolio.xlsx
@@ -515,19 +515,19 @@
         <v>64.75</v>
       </c>
       <c r="G2" t="n">
-        <v>24.7</v>
+        <v>38.75</v>
       </c>
       <c r="H2" t="n">
         <v>388500</v>
       </c>
       <c r="I2" t="n">
-        <v>148200</v>
+        <v>232500</v>
       </c>
       <c r="J2" t="n">
-        <v>-240300</v>
+        <v>-156000</v>
       </c>
       <c r="K2" t="n">
-        <v>-61.85328185328185</v>
+        <v>-40.15444015444015</v>
       </c>
     </row>
     <row r="3">
@@ -556,19 +556,19 @@
         <v>24.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H3" t="n">
         <v>148800</v>
       </c>
       <c r="I3" t="n">
-        <v>31200</v>
+        <v>34800</v>
       </c>
       <c r="J3" t="n">
-        <v>-117600</v>
+        <v>-114000</v>
       </c>
       <c r="K3" t="n">
-        <v>-79.03225806451614</v>
+        <v>-76.61290322580645</v>
       </c>
     </row>
     <row r="4">
@@ -597,19 +597,19 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>13.1</v>
+        <v>18.9</v>
       </c>
       <c r="H4" t="n">
         <v>300000</v>
       </c>
       <c r="I4" t="n">
-        <v>131000</v>
+        <v>189000</v>
       </c>
       <c r="J4" t="n">
-        <v>-169000</v>
+        <v>-111000</v>
       </c>
       <c r="K4" t="n">
-        <v>-56.33333333333334</v>
+        <v>-37.00000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -638,19 +638,19 @@
         <v>10.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H5" t="n">
         <v>1212000</v>
       </c>
       <c r="I5" t="n">
-        <v>780000</v>
+        <v>792000</v>
       </c>
       <c r="J5" t="n">
-        <v>-431999.9999999999</v>
+        <v>-420000</v>
       </c>
       <c r="K5" t="n">
-        <v>-35.64356435643564</v>
+        <v>-34.65346534653465</v>
       </c>
     </row>
     <row r="6">
@@ -679,19 +679,19 @@
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="H6" t="n">
         <v>990000</v>
       </c>
       <c r="I6" t="n">
-        <v>632500</v>
+        <v>676500</v>
       </c>
       <c r="J6" t="n">
-        <v>-357500</v>
+        <v>-313499.9999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-36.11111111111111</v>
+        <v>-31.66666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -720,19 +720,19 @@
         <v>12.7</v>
       </c>
       <c r="G7" t="n">
-        <v>9.35</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
         <v>571500</v>
       </c>
       <c r="I7" t="n">
-        <v>420750</v>
+        <v>450000</v>
       </c>
       <c r="J7" t="n">
-        <v>-150750</v>
+        <v>-121500</v>
       </c>
       <c r="K7" t="n">
-        <v>-26.37795275590551</v>
+        <v>-21.25984251968503</v>
       </c>
     </row>
     <row r="8">
@@ -761,19 +761,19 @@
         <v>7.75</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
         <v>534750</v>
       </c>
       <c r="I8" t="n">
-        <v>441600</v>
+        <v>469200</v>
       </c>
       <c r="J8" t="n">
-        <v>-93149.99999999997</v>
+        <v>-65550.00000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-17.41935483870967</v>
+        <v>-12.25806451612903</v>
       </c>
     </row>
     <row r="9">
@@ -799,22 +799,22 @@
         <v>75000</v>
       </c>
       <c r="F9" t="n">
-        <v>15.312</v>
+        <v>15.4</v>
       </c>
       <c r="G9" t="n">
-        <v>9.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="H9" t="n">
-        <v>1148400</v>
+        <v>1155000</v>
       </c>
       <c r="I9" t="n">
-        <v>697500</v>
+        <v>618750</v>
       </c>
       <c r="J9" t="n">
-        <v>-450899.9999999999</v>
+        <v>-536250</v>
       </c>
       <c r="K9" t="n">
-        <v>-39.26332288401253</v>
+        <v>-46.42857142857143</v>
       </c>
     </row>
     <row r="10">
@@ -843,19 +843,19 @@
         <v>7.45</v>
       </c>
       <c r="G10" t="n">
-        <v>4.66</v>
+        <v>4.32</v>
       </c>
       <c r="H10" t="n">
         <v>201150</v>
       </c>
       <c r="I10" t="n">
-        <v>125820</v>
+        <v>116640</v>
       </c>
       <c r="J10" t="n">
-        <v>-75330</v>
+        <v>-84510</v>
       </c>
       <c r="K10" t="n">
-        <v>-37.4496644295302</v>
+        <v>-42.01342281879194</v>
       </c>
     </row>
     <row r="11">
@@ -884,19 +884,19 @@
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>34</v>
+        <v>36.5</v>
       </c>
       <c r="H11" t="n">
         <v>240000</v>
       </c>
       <c r="I11" t="n">
-        <v>255000</v>
+        <v>273750</v>
       </c>
       <c r="J11" t="n">
-        <v>15000</v>
+        <v>33750</v>
       </c>
       <c r="K11" t="n">
-        <v>6.25</v>
+        <v>14.0625</v>
       </c>
     </row>
     <row r="12">
@@ -925,19 +925,19 @@
         <v>4.48</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="H12" t="n">
         <v>470400</v>
       </c>
       <c r="I12" t="n">
-        <v>191100</v>
+        <v>216300</v>
       </c>
       <c r="J12" t="n">
-        <v>-279300</v>
+        <v>-254100</v>
       </c>
       <c r="K12" t="n">
-        <v>-59.375</v>
+        <v>-54.01785714285715</v>
       </c>
     </row>
     <row r="13">
@@ -1007,19 +1007,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6</v>
+        <v>7.65</v>
       </c>
       <c r="H14" t="n">
         <v>435000</v>
       </c>
       <c r="I14" t="n">
-        <v>330000</v>
+        <v>382500</v>
       </c>
       <c r="J14" t="n">
-        <v>-105000</v>
+        <v>-52499.99999999995</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.13793103448275</v>
+        <v>-12.06896551724137</v>
       </c>
     </row>
     <row r="15">
@@ -1048,19 +1048,19 @@
         <v>12.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="H15" t="n">
         <v>246000</v>
       </c>
       <c r="I15" t="n">
-        <v>206000</v>
+        <v>216000</v>
       </c>
       <c r="J15" t="n">
-        <v>-40000</v>
+        <v>-30000</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.26016260162601</v>
+        <v>-12.19512195121951</v>
       </c>
     </row>
     <row r="16">
@@ -1083,25 +1083,25 @@
         <v>46080</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F16" t="n">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="G16" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="H16" t="n">
-        <v>38000</v>
+        <v>142000</v>
       </c>
       <c r="I16" t="n">
-        <v>36000</v>
+        <v>140000</v>
       </c>
       <c r="J16" t="n">
         <v>-2000</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.263157894736842</v>
+        <v>-1.408450704225352</v>
       </c>
     </row>
     <row r="17">
@@ -1130,19 +1130,19 @@
         <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="H17" t="n">
         <v>44400</v>
       </c>
       <c r="I17" t="n">
-        <v>17160</v>
+        <v>16440</v>
       </c>
       <c r="J17" t="n">
-        <v>-27240</v>
+        <v>-27960</v>
       </c>
       <c r="K17" t="n">
-        <v>-61.35135135135135</v>
+        <v>-62.97297297297298</v>
       </c>
     </row>
     <row r="18">
@@ -1171,19 +1171,19 @@
         <v>4.96</v>
       </c>
       <c r="G18" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H18" t="n">
         <v>44640</v>
       </c>
       <c r="I18" t="n">
-        <v>18720</v>
+        <v>19260</v>
       </c>
       <c r="J18" t="n">
-        <v>-25920</v>
+        <v>-25380</v>
       </c>
       <c r="K18" t="n">
-        <v>-58.06451612903226</v>
+        <v>-56.85483870967742</v>
       </c>
     </row>
     <row r="19">
@@ -1212,19 +1212,19 @@
         <v>21.7</v>
       </c>
       <c r="G19" t="n">
-        <v>9.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>86800</v>
       </c>
       <c r="I19" t="n">
-        <v>39000</v>
+        <v>37200</v>
       </c>
       <c r="J19" t="n">
-        <v>-47800</v>
+        <v>-49599.99999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-55.06912442396313</v>
+        <v>-57.14285714285714</v>
       </c>
     </row>
     <row r="20">
@@ -1294,19 +1294,19 @@
         <v>11.4</v>
       </c>
       <c r="G21" t="n">
-        <v>8.6</v>
+        <v>7.75</v>
       </c>
       <c r="H21" t="n">
         <v>41040</v>
       </c>
       <c r="I21" t="n">
-        <v>30960</v>
+        <v>27900</v>
       </c>
       <c r="J21" t="n">
-        <v>-10080</v>
+        <v>-13140</v>
       </c>
       <c r="K21" t="n">
-        <v>-24.56140350877194</v>
+        <v>-32.01754385964913</v>
       </c>
     </row>
     <row r="22">
@@ -1335,19 +1335,19 @@
         <v>38.78</v>
       </c>
       <c r="G22" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="H22" t="n">
         <v>1047060</v>
       </c>
       <c r="I22" t="n">
-        <v>850500</v>
+        <v>864000</v>
       </c>
       <c r="J22" t="n">
-        <v>-196560</v>
+        <v>-183060</v>
       </c>
       <c r="K22" t="n">
-        <v>-18.77256317689531</v>
+        <v>-17.48323878287777</v>
       </c>
     </row>
     <row r="23">
@@ -1376,19 +1376,19 @@
         <v>26.4</v>
       </c>
       <c r="G23" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="H23" t="n">
         <v>462000</v>
       </c>
       <c r="I23" t="n">
-        <v>159250</v>
+        <v>173250</v>
       </c>
       <c r="J23" t="n">
-        <v>-302749.9999999999</v>
+        <v>-288750</v>
       </c>
       <c r="K23" t="n">
-        <v>-65.53030303030302</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="24">
@@ -1417,19 +1417,19 @@
         <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>14.4</v>
+        <v>12.4</v>
       </c>
       <c r="H24" t="n">
         <v>26000</v>
       </c>
       <c r="I24" t="n">
-        <v>14400</v>
+        <v>12400</v>
       </c>
       <c r="J24" t="n">
-        <v>-11600</v>
+        <v>-13600</v>
       </c>
       <c r="K24" t="n">
-        <v>-44.61538461538462</v>
+        <v>-52.30769230769231</v>
       </c>
     </row>
     <row r="25">
@@ -1458,19 +1458,19 @@
         <v>24.9</v>
       </c>
       <c r="G25" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="H25" t="n">
         <v>99600</v>
       </c>
       <c r="I25" t="n">
-        <v>96400</v>
+        <v>96800</v>
       </c>
       <c r="J25" t="n">
-        <v>-3199.999999999989</v>
+        <v>-2799.999999999997</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.212851405622478</v>
+        <v>-2.811244979919676</v>
       </c>
     </row>
     <row r="26">
@@ -1499,19 +1499,19 @@
         <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>19.2</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
         <v>288000</v>
       </c>
       <c r="I26" t="n">
-        <v>138240</v>
+        <v>172800</v>
       </c>
       <c r="J26" t="n">
-        <v>-149760</v>
+        <v>-115200</v>
       </c>
       <c r="K26" t="n">
-        <v>-52</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="27">
@@ -1540,19 +1540,19 @@
         <v>37.7</v>
       </c>
       <c r="G27" t="n">
-        <v>8.85</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
         <v>263900</v>
       </c>
       <c r="I27" t="n">
-        <v>61950</v>
+        <v>70000</v>
       </c>
       <c r="J27" t="n">
-        <v>-201950</v>
+        <v>-193900</v>
       </c>
       <c r="K27" t="n">
-        <v>-76.52519893899205</v>
+        <v>-73.47480106100797</v>
       </c>
     </row>
     <row r="28">
@@ -1581,19 +1581,19 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H28" t="n">
         <v>450000</v>
       </c>
       <c r="I28" t="n">
-        <v>91500</v>
+        <v>89500</v>
       </c>
       <c r="J28" t="n">
-        <v>-358500</v>
+        <v>-360500</v>
       </c>
       <c r="K28" t="n">
-        <v>-79.66666666666666</v>
+        <v>-80.11111111111111</v>
       </c>
     </row>
   </sheetData>
